--- a/src/components/study/excel/topics/004_001_modern-lookup-and-dynamic-array-functions/excel_files/dynamic_arrays_master.xlsx
+++ b/src/components/study/excel/topics/004_001_modern-lookup-and-dynamic-array-functions/excel_files/dynamic_arrays_master.xlsx
@@ -2197,7 +2197,7 @@
       <c r="F42" s="14"/>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" algorithmName="SHA-512" hashValue="i6V3yM7NdvnNfb5WyfMKbCDUX0VNWWm3wVEUlcnNM6qse9ZXbUZSTbjj6KMm+6pYP+DrhTmhcN0maT8G7w9esQ==" saltValue="qJHL+Poyu9G+4E6H2XOC7g==" spinCount="100000"/>
+  <sheetProtection sheet="1" algorithmName="SHA-512" hashValue="N8EZlngk2hVBnT8BVbHjDT6XoOK4kU7WG2W9Dh/sNDpbzz05FVuMlgZTGPOsgSMa22lq/WRRobO3h+Rfuis8PQ==" saltValue="nVHx77cyVv2h5eZsJUsl+Q==" spinCount="100000"/>
   <mergeCells count="48">
     <mergeCell ref="C1:F2"/>
     <mergeCell ref="C3:F3"/>
